--- a/Cases/Outputs/Case_LR_summary.xlsx
+++ b/Cases/Outputs/Case_LR_summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huncho/Desktop/Forensic_Kinship_Project/Cases/Original_Files/White_British_Cases/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huncho/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C540A2C7-10BE-3744-96AE-84F65CCB96FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCC93B20-ED41-664A-9084-D6B8FEB87963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2540" yWindow="620" windowWidth="14180" windowHeight="16300" xr2:uid="{21908E20-FA92-AA47-A126-C102B85F67AE}"/>
+    <workbookView xWindow="2520" yWindow="500" windowWidth="14180" windowHeight="16260" xr2:uid="{21908E20-FA92-AA47-A126-C102B85F67AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Case_LR_summary_classified" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>case</t>
   </si>
@@ -38,12 +38,6 @@
   </si>
   <si>
     <t>LR_HS</t>
-  </si>
-  <si>
-    <t>log10LR_FC</t>
-  </si>
-  <si>
-    <t>log10LR_HS</t>
   </si>
   <si>
     <t>LR_FCvsHS</t>
@@ -575,12 +569,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -643,13 +638,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
@@ -1126,14 +1121,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B17D794-2873-7A48-8142-2DFBECE00DEA}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="9" max="9" width="14.1640625" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1152,22 +1147,16 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="B2">
         <v>-20247.833999999999</v>
@@ -1184,19 +1173,13 @@
       <c r="F2" s="1">
         <v>3.0600000000000003E-29</v>
       </c>
-      <c r="G2">
-        <v>-13.256839060000001</v>
-      </c>
-      <c r="H2">
-        <v>-28.5144728</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>-20273.716</v>
@@ -1213,19 +1196,13 @@
       <c r="F3" s="1">
         <v>3.7299999999999998E-30</v>
       </c>
-      <c r="G3">
-        <v>-14.08503864</v>
-      </c>
-      <c r="H3">
-        <v>-29.427794089999999</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>13</v>
       </c>
       <c r="B4">
         <v>-19833.626</v>
@@ -1236,31 +1213,25 @@
       <c r="D4">
         <v>-20095.409</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>4.9100000000000001E+113</v>
       </c>
       <c r="F4" s="1">
         <v>9.1700000000000002E+107</v>
       </c>
-      <c r="G4" s="3">
-        <v>113.6909124</v>
-      </c>
-      <c r="H4">
-        <v>107.9621338</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="4">
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="4">
         <v>535523.47208395402</v>
       </c>
-      <c r="K4" s="4">
+      <c r="I4" s="4">
         <v>5.7287785107853102</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>-19964.955999999998</v>
@@ -1271,31 +1242,25 @@
       <c r="D5">
         <v>-20269.542000000001</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="5">
         <v>1.9100000000000002E+132</v>
       </c>
       <c r="F5" s="1">
         <v>6.6199999999999997E+127</v>
       </c>
-      <c r="G5" s="3">
-        <v>132.2800191</v>
-      </c>
-      <c r="H5">
-        <v>127.82111759999999</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4">
+        <v>28767.455217835799</v>
+      </c>
+      <c r="I5" s="4">
+        <v>4.4589014457021898</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>14</v>
-      </c>
-      <c r="J5" s="4">
-        <v>28767.455217835799</v>
-      </c>
-      <c r="K5" s="4">
-        <v>4.4589014457021898</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>16</v>
       </c>
       <c r="B6">
         <v>-20151.833999999999</v>
@@ -1312,19 +1277,13 @@
       <c r="F6" s="1">
         <v>4.3300000000000001E-28</v>
       </c>
-      <c r="G6">
-        <v>-12.234075560000001</v>
-      </c>
-      <c r="H6">
-        <v>-27.363158129999999</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>11</v>
+      <c r="G6" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>-20176.324000000001</v>
@@ -1341,14 +1300,8 @@
       <c r="F7" s="1">
         <v>3.69E-28</v>
       </c>
-      <c r="G7">
-        <v>-12.45513145</v>
-      </c>
-      <c r="H7">
-        <v>-27.433513829999999</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>11</v>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
